--- a/results/gmac_snr6dB/gmac_snr6dB_classC_Ru33_Rv64_SCL32/classC_Ru33_Rv64_snr6dB_SCL_L32.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classC_Ru33_Rv64_SCL32/classC_Ru33_Rv64_snr6dB_SCL_L32.xlsx
@@ -473,7 +473,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gaussian MAC — Class C, (Ru=0.33, Rv=0.64), SNR=6dB, SCL (L=32), analytic design</t>
+          <t>Gaussian MAC — Class C, (Ru=0.33, Rv=0.64), SNR=6dB, SCL (L=32)</t>
         </is>
       </c>
     </row>
